--- a/NordPush-SEO-Audit-2026-04-23.xlsx
+++ b/NordPush-SEO-Audit-2026-04-23.xlsx
@@ -682,8 +682,10 @@
           <t>Hoher Impact</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>3</v>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>3 (1 behoben, 2 offen)</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -906,9 +908,9 @@
       <c r="H4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Offen</t>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Behoben</t>
         </is>
       </c>
     </row>

--- a/NordPush-SEO-Audit-2026-04-23.xlsx
+++ b/NordPush-SEO-Audit-2026-04-23.xlsx
@@ -694,8 +694,10 @@
           <t>Mittlerer Impact</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>3</v>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>3 (1 behoben, 2 offen)</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -994,9 +996,9 @@
       <c r="H6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Offen</t>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Behoben</t>
         </is>
       </c>
     </row>

--- a/NordPush-SEO-Audit-2026-04-23.xlsx
+++ b/NordPush-SEO-Audit-2026-04-23.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>3 (1 behoben, 2 offen)</t>
+          <t>3 (2 behoben, 1 offen)</t>
         </is>
       </c>
     </row>
@@ -1082,9 +1082,9 @@
       <c r="H8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Offen</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Behoben</t>
         </is>
       </c>
     </row>

--- a/NordPush-SEO-Audit-2026-04-23.xlsx
+++ b/NordPush-SEO-Audit-2026-04-23.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Maßnahmenplan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zusammenfassung'!$A$4:$B$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Befunde'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zusammenfassung'!$A$4:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Befunde'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Was läuft gut'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Maßnahmenplan'!$A$1:$F$8</definedName>
   </definedNames>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -696,22 +696,34 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>3 (2 behoben, 1 offen)</t>
+          <t>4 (4 behoben, 0 offen)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Niedrig-Impact</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2 (1 behoben, 1 zurückgestellt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Bestandene Prüfungen</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B15" s="5" t="n">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B14"/>
+  <autoFilter ref="A4:B15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
@@ -726,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1131,8 +1143,94 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>On-Page</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>MITTEL</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Drei Titles überschreiten Sistrix-Pixel-Limit (477 px)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>MITTEL</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>/seo-audit/ ~623 px, /keyword-recherche/ ~647 px, /seo-monitoring/ ~626 px — alle werden in Google-SERP abgeschnitten</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>services/[slug]/page.tsx: forceOverride-Map für die 3 Slugs mit pixel-safen Alternativen (≤ 475 px)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Behoben</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Strukturierte Daten</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>NIEDRIG</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>/wordpress-seo/ fehlt FAQPage-Schema</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>NIEDRIG-MITTEL</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Alle 21 anderen Service-Seiten haben BreadcrumbList+Service+FAQPage; /wordpress-seo/ nur BreadcrumbList+Service</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>services/[slug]/page.tsx: FAQ-Ableitung aus page-content.ts bei ContentPage-Fallback ergänzen, damit baseFaqs ins Schema einfließen</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Behoben</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
